--- a/files/港岛-寿臣山-寿臣山15号.xlsx
+++ b/files/港岛-寿臣山-寿臣山15号.xlsx
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>2746</v>
+        <v>3823</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
         <v>259964000</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>94670</v>
+        <v>68000</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>4759</v>
+        <v>4726</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>435000000</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>91406</v>
+        <v>92044</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4696</v>
+        <v>4831</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>289860000</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>61725</v>
+        <v>60000</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
@@ -1925,10 +1925,10 @@
       <c r="B7" s="17" t="inlineStr">
         <is>
           <t>8号屋
-2746呎 (4+房)
+3823呎 (4+房)
 (24年-05月-22日)
 $2.60亿
-$94,670/呎</t>
+$68,000/呎</t>
         </is>
       </c>
       <c r="C7" s="17" t="inlineStr">
@@ -1952,10 +1952,10 @@
       <c r="E7" s="17" t="inlineStr">
         <is>
           <t>11号屋
-4759呎 (4+房)
+4726呎 (4+房)
 (22年-08月-08日)
 $4.35亿
-$91,406/呎</t>
+$92,044/呎</t>
         </is>
       </c>
       <c r="F7" s="17" t="inlineStr">
@@ -1970,10 +1970,10 @@
       <c r="G7" s="17" t="inlineStr">
         <is>
           <t>15号屋
-4696呎 (4+房)
+4831呎 (4+房)
 (26年-01月-07日)
 $2.90亿
-$61,725/呎</t>
+$60,000/呎</t>
         </is>
       </c>
     </row>
